--- a/detected_malicious_models.xlsx
+++ b/detected_malicious_models.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ML_Project_2026\ACSAC\1.final_artifacts\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3E63E2-4A37-414C-95A7-9C53FC597294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761DC3D6-F5A7-4EC4-9330-63A670E26272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{04670FFF-DBFA-4277-80BE-E624778C8932}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{04670FFF-DBFA-4277-80BE-E624778C8932}"/>
   </bookViews>
   <sheets>
     <sheet name="41_Malicious Models" sheetId="1" r:id="rId1"/>
     <sheet name="Low-Impact 65 Malicious Models" sheetId="2" r:id="rId2"/>
     <sheet name="105 New Malicious Models " sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4530,21 +4529,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4555,6 +4539,24 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4564,9 +4566,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4953,11 +4952,11 @@
       <c r="D1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="47" t="s">
         <v>881</v>
       </c>
-      <c r="F1" s="51"/>
-      <c r="G1" s="47" t="s">
+      <c r="F1" s="47"/>
+      <c r="G1" s="48" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="46" t="s">
@@ -4968,7 +4967,7 @@
       </c>
       <c r="J1" s="46"/>
       <c r="K1" s="46"/>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="47" t="s">
         <v>41</v>
       </c>
       <c r="M1" s="46" t="s">
@@ -5010,7 +5009,7 @@
       <c r="F2" s="36" t="s">
         <v>883</v>
       </c>
-      <c r="G2" s="47"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="46"/>
       <c r="I2" s="35" t="s">
         <v>40</v>
@@ -5021,7 +5020,7 @@
       <c r="K2" s="36" t="s">
         <v>908</v>
       </c>
-      <c r="L2" s="51"/>
+      <c r="L2" s="47"/>
       <c r="M2" s="38" t="s">
         <v>56</v>
       </c>
@@ -7974,11 +7973,11 @@
       </c>
     </row>
     <row r="45" spans="1:23" ht="57.6" customHeight="1">
-      <c r="A45" s="48" t="s">
+      <c r="A45" s="43" t="s">
         <v>884</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="50"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="45"/>
       <c r="G45" s="12"/>
       <c r="M45" s="27"/>
       <c r="N45" s="28"/>
@@ -8006,12 +8005,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="E1:F1"/>
     <mergeCell ref="W1:W2"/>
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="T1:T2"/>
@@ -8024,6 +8017,12 @@
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="E1:F1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{AB12B4A2-43F7-4CA7-827D-F11FE676A967}"/>
@@ -8090,32 +8089,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>881</v>
       </c>
-      <c r="G1" s="44"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:13" ht="18">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
       <c r="F2" s="42" t="s">
         <v>882</v>
       </c>
@@ -10135,81 +10134,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="31" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="54" t="s">
         <v>909</v>
       </c>
-      <c r="F1" s="54"/>
-      <c r="G1" s="52" t="s">
+      <c r="F1" s="55"/>
+      <c r="G1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55" t="s">
+      <c r="J1" s="52"/>
+      <c r="K1" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="47" t="s">
+      <c r="L1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47" t="s">
+      <c r="M1" s="48"/>
+      <c r="N1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47" t="s">
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48" t="s">
         <v>504</v>
       </c>
-      <c r="R1" s="47" t="s">
+      <c r="R1" s="48" t="s">
         <v>541</v>
       </c>
-      <c r="S1" s="47" t="s">
+      <c r="S1" s="48" t="s">
         <v>543</v>
       </c>
-      <c r="T1" s="47" t="s">
+      <c r="T1" s="48" t="s">
         <v>542</v>
       </c>
-      <c r="U1" s="47" t="s">
+      <c r="U1" s="48" t="s">
         <v>528</v>
       </c>
-      <c r="V1" s="47"/>
+      <c r="V1" s="48"/>
     </row>
     <row r="2" spans="1:22" s="31" customFormat="1" ht="18">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
       <c r="E2" s="34" t="s">
         <v>882</v>
       </c>
       <c r="F2" s="34" t="s">
         <v>883</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="55"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="J2" s="32" t="s">
         <v>549</v>
       </c>
-      <c r="K2" s="55"/>
+      <c r="K2" s="52"/>
       <c r="L2" s="32" t="s">
         <v>56</v>
       </c>
@@ -10225,12 +10224,12 @@
       <c r="P2" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
     </row>
     <row r="3" spans="1:22" s="19" customFormat="1" ht="43.2">
       <c r="A3" s="19" t="s">
@@ -17076,11 +17075,11 @@
       <c r="U109" s="20"/>
     </row>
     <row r="110" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A110" s="48" t="s">
+      <c r="A110" s="43" t="s">
         <v>1036</v>
       </c>
-      <c r="B110" s="49"/>
-      <c r="C110" s="50"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="45"/>
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" s="12"/>
@@ -17131,6 +17130,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="Q1:Q2"/>
@@ -17140,15 +17148,6 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="K1:K2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" xr:uid="{E3C7E6AE-7D08-45CE-A193-AA3D6DF2D5B3}"/>
@@ -17256,13 +17255,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId102"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6B5BE2-31E2-4467-8856-7F88B7E35BD8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>